--- a/templates/sanitized/guide-ds.xlsx
+++ b/templates/sanitized/guide-ds.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">세부내역!$A$1:$L$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">세부내역!$1:$3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <customWorkbookViews>
     <customWorkbookView name="박수백 - 사용자 보기" guid="{1FA04683-E8B6-40FB-A56A-4A427B1A01C5}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" tabRatio="823" activeSheetId="1"/>
   </customWorkbookViews>
@@ -3340,9 +3340,8 @@
       <c r="B8" s="126" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="44" t="str">
+      <c r="C8" s="44">
         <f>"일금"&amp;NUMBERSTRING(H12,1)&amp;"원정(\"&amp;TEXT(H12,"###,##0")&amp;") V.A.T별도"</f>
-        <v>일금사백삼십구만일천원정(\4,391,000) V.A.T별도</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -3416,11 +3415,9 @@
       </c>
       <c r="G11" s="53">
         <f>세부내역!K27</f>
-        <v>4391729</v>
       </c>
       <c r="H11" s="53">
         <f>F11*G11</f>
-        <v>4391729</v>
       </c>
       <c r="I11" s="46"/>
       <c r="J11" s="2"/>
@@ -3437,7 +3434,6 @@
       <c r="G12" s="182"/>
       <c r="H12" s="182">
         <f>ROUNDDOWN(SUM(H11:H11),-3)</f>
-        <v>4391000</v>
       </c>
       <c r="I12" s="183" t="s">
         <v>42</v>
@@ -3632,9 +3628,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" s="77" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="A1" s="230" t="str">
+      <c r="A1" s="230">
         <f>"▣ 공사명 : "&amp;갑지!C5</f>
-        <v>▣ 공사명 : 설치 or 공사 끝맺음</v>
       </c>
       <c r="B1" s="230"/>
       <c r="C1" s="230"/>
@@ -4023,18 +4018,10 @@
       <c r="E6" s="140"/>
       <c r="F6" s="141"/>
       <c r="G6" s="142"/>
-      <c r="H6" s="138">
-        <f t="shared" ref="H6:H14" si="0">G6*F6</f>
-      </c>
-      <c r="I6" s="138">
-        <f t="shared" ref="I6" si="1">INT(SUM((R6*S6),S6)*Q6)</f>
-      </c>
-      <c r="J6" s="140">
-        <f t="shared" ref="J6:J14" si="2">F6*I6</f>
-      </c>
-      <c r="K6" s="138">
-        <f t="shared" ref="K6" si="3">J6+H6</f>
-      </c>
+      <c r="H6" s="138"/>
+      <c r="I6" s="138"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="138"/>
       <c r="L6" s="143"/>
       <c r="M6" s="156"/>
       <c r="N6" s="153"/>
@@ -4042,104 +4029,54 @@
       <c r="P6" s="144"/>
       <c r="Q6" s="145"/>
       <c r="R6" s="146"/>
-      <c r="S6" s="147">
-        <f t="shared" ref="S6" si="4">SUM(U6,W6,Y6,AA6,AC6,AE6,AG6,AI6,AK6,AM6,AO6,AQ6,AS6,AU6,AW6,AY6,BA6)</f>
-      </c>
-      <c r="T6" s="148">
-        <f t="shared" ref="T6" si="5">0.7+0.59</f>
-      </c>
-      <c r="U6" s="147">
-        <f t="shared" ref="U6" si="6">T6*U$3</f>
-      </c>
-      <c r="V6" s="148">
-        <f t="shared" ref="V6" si="7">0.5+0.3+0.7+0.89</f>
-      </c>
-      <c r="W6" s="147">
-        <f t="shared" ref="W6" si="8">V6*W$3</f>
-      </c>
+      <c r="S6" s="147"/>
+      <c r="T6" s="148"/>
+      <c r="U6" s="147"/>
+      <c r="V6" s="148"/>
+      <c r="W6" s="147"/>
       <c r="X6" s="148"/>
-      <c r="Y6" s="147">
-        <f t="shared" ref="Y6" si="9">X6*Y$3</f>
-      </c>
+      <c r="Y6" s="147"/>
       <c r="Z6" s="148"/>
-      <c r="AA6" s="147">
-        <f t="shared" ref="AA6" si="10">Z6*AA$3</f>
-      </c>
+      <c r="AA6" s="147"/>
       <c r="AB6" s="149"/>
-      <c r="AC6" s="147">
-        <f t="shared" ref="AC6" si="11">AB6*AC$3</f>
-      </c>
+      <c r="AC6" s="147"/>
       <c r="AD6" s="150"/>
-      <c r="AE6" s="147">
-        <f t="shared" ref="AE6" si="12">AD6*AE$3</f>
-      </c>
+      <c r="AE6" s="147"/>
       <c r="AF6" s="150"/>
-      <c r="AG6" s="147">
-        <f t="shared" ref="AG6" si="13">AF6*AG$3</f>
-      </c>
+      <c r="AG6" s="147"/>
       <c r="AH6" s="150"/>
-      <c r="AI6" s="147">
-        <f t="shared" ref="AI6" si="14">AH6*AI$3</f>
-      </c>
+      <c r="AI6" s="147"/>
       <c r="AJ6" s="150"/>
-      <c r="AK6" s="147">
-        <f t="shared" ref="AK6" si="15">AJ6*AK$3</f>
-      </c>
+      <c r="AK6" s="147"/>
       <c r="AL6" s="150"/>
-      <c r="AM6" s="147">
-        <f t="shared" ref="AM6" si="16">AL6*AM$3</f>
-      </c>
+      <c r="AM6" s="147"/>
       <c r="AN6" s="150"/>
-      <c r="AO6" s="147">
-        <f t="shared" ref="AO6" si="17">AN6*AO$3</f>
-      </c>
+      <c r="AO6" s="147"/>
       <c r="AP6" s="150"/>
-      <c r="AQ6" s="147">
-        <f t="shared" ref="AQ6" si="18">AP6*AQ$3</f>
-      </c>
+      <c r="AQ6" s="147"/>
       <c r="AR6" s="150"/>
-      <c r="AS6" s="147">
-        <f t="shared" ref="AS6" si="19">AR6*AS$3</f>
-      </c>
+      <c r="AS6" s="147"/>
       <c r="AT6" s="150"/>
-      <c r="AU6" s="147">
-        <f t="shared" ref="AU6" si="20">AT6*AU$3</f>
-      </c>
+      <c r="AU6" s="147"/>
       <c r="AV6" s="150"/>
-      <c r="AW6" s="147">
-        <f t="shared" ref="AW6" si="21">AV6*AW$3</f>
-      </c>
+      <c r="AW6" s="147"/>
       <c r="AX6" s="149"/>
-      <c r="AY6" s="147">
-        <f t="shared" ref="AY6" si="22">AX6*AY$3</f>
-      </c>
+      <c r="AY6" s="147"/>
       <c r="AZ6" s="151"/>
-      <c r="BA6" s="147">
-        <f t="shared" ref="BA6" si="23">AZ6*BA$3</f>
-      </c>
+      <c r="BA6" s="147"/>
     </row>
     <row r="7" spans="1:53" ht="21" customHeight="1">
-      <c r="A7" s="82">
-        <f>A6+1</f>
-      </c>
+      <c r="A7" s="82"/>
       <c r="B7" s="26"/>
       <c r="C7" s="76"/>
       <c r="D7" s="129"/>
       <c r="E7" s="59"/>
-      <c r="F7" s="57">
-        <f>F6</f>
-      </c>
+      <c r="F7" s="57"/>
       <c r="G7" s="22"/>
-      <c r="H7" s="22">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H7" s="22"/>
       <c r="I7" s="22"/>
-      <c r="J7" s="58">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="K7" s="22">
-        <f t="shared" ref="K7" si="24">+H7+J7</f>
-      </c>
+      <c r="J7" s="58"/>
+      <c r="K7" s="22"/>
       <c r="L7" s="103"/>
       <c r="M7" s="165"/>
       <c r="N7" s="161"/>
@@ -4183,27 +4120,17 @@
       <c r="BA7" s="161"/>
     </row>
     <row r="8" spans="1:53" ht="21" customHeight="1">
-      <c r="A8" s="82">
-        <f t="shared" ref="A8:A14" si="25">A7+1</f>
-      </c>
+      <c r="A8" s="82"/>
       <c r="B8" s="26"/>
       <c r="C8" s="76"/>
       <c r="D8" s="129"/>
       <c r="E8" s="59"/>
-      <c r="F8" s="57">
-        <f>F6</f>
-      </c>
+      <c r="F8" s="57"/>
       <c r="G8" s="23"/>
-      <c r="H8" s="22">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H8" s="22"/>
       <c r="I8" s="22"/>
-      <c r="J8" s="58">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="K8" s="22">
-        <f t="shared" ref="K8:K14" si="26">+H8+J8</f>
-      </c>
+      <c r="J8" s="58"/>
+      <c r="K8" s="22"/>
       <c r="L8" s="103"/>
       <c r="M8" s="165"/>
       <c r="N8" s="161"/>
@@ -4247,27 +4174,17 @@
       <c r="BA8" s="161"/>
     </row>
     <row r="9" spans="1:53" ht="21" customHeight="1">
-      <c r="A9" s="82">
-        <f t="shared" si="25"/>
-      </c>
+      <c r="A9" s="82"/>
       <c r="B9" s="56"/>
       <c r="C9" s="76"/>
       <c r="D9" s="129"/>
       <c r="E9" s="59"/>
-      <c r="F9" s="57">
-        <f>F6</f>
-      </c>
+      <c r="F9" s="57"/>
       <c r="G9" s="22"/>
-      <c r="H9" s="22">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H9" s="22"/>
       <c r="I9" s="22"/>
-      <c r="J9" s="58">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="K9" s="22">
-        <f t="shared" si="26"/>
-      </c>
+      <c r="J9" s="58"/>
+      <c r="K9" s="22"/>
       <c r="L9" s="117"/>
       <c r="M9" s="165"/>
       <c r="N9" s="161"/>
@@ -4311,27 +4228,17 @@
       <c r="BA9" s="161"/>
     </row>
     <row r="10" spans="1:53" ht="21" customHeight="1">
-      <c r="A10" s="82">
-        <f t="shared" si="25"/>
-      </c>
+      <c r="A10" s="82"/>
       <c r="B10" s="76"/>
       <c r="C10" s="80"/>
       <c r="D10" s="130"/>
       <c r="E10" s="55"/>
-      <c r="F10" s="61">
-        <f>F6</f>
-      </c>
+      <c r="F10" s="61"/>
       <c r="G10" s="22"/>
-      <c r="H10" s="22">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H10" s="22"/>
       <c r="I10" s="22"/>
-      <c r="J10" s="58">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="K10" s="22">
-        <f t="shared" si="26"/>
-      </c>
+      <c r="J10" s="58"/>
+      <c r="K10" s="22"/>
       <c r="L10" s="117"/>
       <c r="M10" s="166"/>
       <c r="N10" s="161"/>
@@ -4375,27 +4282,17 @@
       <c r="BA10" s="161"/>
     </row>
     <row r="11" spans="1:53" ht="21" customHeight="1">
-      <c r="A11" s="82">
-        <f t="shared" si="25"/>
-      </c>
+      <c r="A11" s="82"/>
       <c r="B11" s="56"/>
       <c r="C11" s="62"/>
       <c r="D11" s="131"/>
       <c r="E11" s="58"/>
-      <c r="F11" s="57">
-        <f>F6</f>
-      </c>
+      <c r="F11" s="57"/>
       <c r="G11" s="22"/>
-      <c r="H11" s="22">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H11" s="22"/>
       <c r="I11" s="22"/>
-      <c r="J11" s="58">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="K11" s="22">
-        <f t="shared" si="26"/>
-      </c>
+      <c r="J11" s="58"/>
+      <c r="K11" s="22"/>
       <c r="L11" s="117"/>
       <c r="M11" s="167"/>
       <c r="N11" s="161"/>
@@ -4439,27 +4336,17 @@
       <c r="BA11" s="161"/>
     </row>
     <row r="12" spans="1:53" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A12" s="82">
-        <f t="shared" si="25"/>
-      </c>
+      <c r="A12" s="82"/>
       <c r="B12" s="73"/>
       <c r="C12" s="105"/>
       <c r="D12" s="132"/>
       <c r="E12" s="81"/>
-      <c r="F12" s="61">
-        <f>F6*2</f>
-      </c>
+      <c r="F12" s="61"/>
       <c r="G12" s="23"/>
-      <c r="H12" s="22">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H12" s="22"/>
       <c r="I12" s="22"/>
-      <c r="J12" s="58">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="K12" s="22">
-        <f t="shared" si="26"/>
-      </c>
+      <c r="J12" s="58"/>
+      <c r="K12" s="22"/>
       <c r="L12" s="118"/>
       <c r="M12" s="168"/>
       <c r="N12" s="162"/>
@@ -4504,8 +4391,7 @@
     </row>
     <row r="13" spans="1:53" s="28" customFormat="1" ht="21" customHeight="1">
       <c r="A13" s="82">
-        <f t="shared" si="25"/>
-        <v>8</v>
+        <f>A12+1</f>
       </c>
       <c r="B13" s="73" t="s">
         <v>30</v>
@@ -4522,20 +4408,16 @@
       </c>
       <c r="G13" s="55">
         <f>H12*40%</f>
-        <v>4800</v>
       </c>
       <c r="H13" s="22">
-        <f t="shared" si="0"/>
-        <v>4800</v>
+        <f>G13*F13</f>
       </c>
       <c r="I13" s="22"/>
       <c r="J13" s="58">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>F13*I13</f>
       </c>
       <c r="K13" s="22">
-        <f t="shared" si="26"/>
-        <v>4800</v>
+        <f>+H13+J13</f>
       </c>
       <c r="L13" s="117"/>
       <c r="M13" s="168"/>
@@ -4581,8 +4463,7 @@
     </row>
     <row r="14" spans="1:53" ht="21" customHeight="1">
       <c r="A14" s="109">
-        <f t="shared" si="25"/>
-        <v>9</v>
+        <f>A13+1</f>
       </c>
       <c r="B14" s="71" t="s">
         <v>21</v>
@@ -4599,20 +4480,16 @@
       </c>
       <c r="G14" s="102">
         <f>INT(SUM(H6:H13)*2%)</f>
-        <v>69936</v>
       </c>
       <c r="H14" s="27">
-        <f t="shared" si="0"/>
-        <v>69936</v>
+        <f>G14*F14</f>
       </c>
       <c r="I14" s="27"/>
       <c r="J14" s="63">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>F14*I14</f>
       </c>
       <c r="K14" s="27">
-        <f t="shared" si="26"/>
-        <v>69936</v>
+        <f>+H14+J14</f>
       </c>
       <c r="L14" s="116"/>
       <c r="M14" s="169"/>
@@ -4668,16 +4545,13 @@
       <c r="G15" s="200"/>
       <c r="H15" s="200">
         <f>SUM(H6:H14)</f>
-        <v>3566736</v>
       </c>
       <c r="I15" s="200"/>
       <c r="J15" s="200">
         <f>SUM(J6:J14)</f>
-        <v>288221</v>
       </c>
       <c r="K15" s="200">
         <f>SUM(K6:K14)</f>
-        <v>3854957</v>
       </c>
       <c r="L15" s="201"/>
       <c r="M15" s="100"/>
@@ -4724,7 +4598,6 @@
       <c r="J17" s="25"/>
       <c r="K17" s="25">
         <f>INT(J15*F17)</f>
-        <v>14007</v>
       </c>
       <c r="L17" s="93"/>
       <c r="M17" s="75"/>
@@ -4752,7 +4625,6 @@
       <c r="J18" s="25"/>
       <c r="K18" s="25">
         <f>INT(J15*F18)</f>
-        <v>1222</v>
       </c>
       <c r="L18" s="93"/>
       <c r="M18" s="75"/>
@@ -4780,7 +4652,6 @@
       <c r="J19" s="25"/>
       <c r="K19" s="25">
         <f>INT(J15*F19)</f>
-        <v>2769</v>
       </c>
       <c r="L19" s="93"/>
       <c r="M19" s="75"/>
@@ -4895,7 +4766,6 @@
       <c r="J23" s="25"/>
       <c r="K23" s="175">
         <f>INT(K15*F23)</f>
-        <v>119889</v>
       </c>
       <c r="L23" s="106"/>
       <c r="M23" s="75"/>
@@ -4952,7 +4822,6 @@
       <c r="J25" s="42"/>
       <c r="K25" s="27">
         <f>INT((SUM(K15,K23,K17))*F25)</f>
-        <v>398885</v>
       </c>
       <c r="L25" s="119"/>
       <c r="M25" s="75"/>
@@ -4972,7 +4841,6 @@
       <c r="J26" s="194"/>
       <c r="K26" s="195">
         <f>SUM(K17:K25)</f>
-        <v>536772</v>
       </c>
       <c r="L26" s="196"/>
       <c r="M26" s="202"/>
@@ -4992,7 +4860,6 @@
       <c r="J27" s="184"/>
       <c r="K27" s="188">
         <f>K15+K26</f>
-        <v>4391729</v>
       </c>
       <c r="L27" s="189"/>
       <c r="M27" s="202"/>

--- a/templates/sanitized/guide-ds.xlsx
+++ b/templates/sanitized/guide-ds.xlsx
@@ -3573,16 +3573,6 @@
     </row>
     <row r="22" spans="1:14" ht="10.199999999999999" customHeight="1"/>
   </sheetData>
-  <customSheetViews>
-    <customSheetView guid="{1FA04683-E8B6-40FB-A56A-4A427B1A01C5}" showPageBreaks="1" fitToPage="1" printArea="1" view="pageBreakPreview">
-      <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-      <printOptions horizontalCentered="1"/>
-      <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
-      <headerFooter scaleWithDoc="0">
-        <oddFooter>&amp;C&amp;P / &amp;N&amp;R㈜서울영상테크</oddFooter>
-      </headerFooter>
-    </customSheetView>
-  </customSheetViews>
   <mergeCells count="5">
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B19:B20"/>
@@ -5263,18 +5253,6 @@
     <row r="420" ht="21" customHeight="1"/>
     <row r="421" ht="21" customHeight="1"/>
   </sheetData>
-  <customSheetViews>
-    <customSheetView guid="{1FA04683-E8B6-40FB-A56A-4A427B1A01C5}" showPageBreaks="1" fitToPage="1" printArea="1" view="pageBreakPreview">
-      <pane xSplit="5" ySplit="3" topLeftCell="F4" activePane="bottomRight" state="frozen"/>
-      <selection pane="bottomRight" activeCell="B16" sqref="B16"/>
-      <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.74803149606299213" bottom="0.51181102362204722" header="0.31496062992125984" footer="0.31496062992125984"/>
-      <printOptions horizontalCentered="1"/>
-      <pageSetup paperSize="9" scale="82" fitToHeight="0" orientation="landscape"/>
-      <headerFooter scaleWithDoc="0">
-        <oddFooter>&amp;C&amp;P / &amp;N&amp;R㈜서울영상테크</oddFooter>
-      </headerFooter>
-    </customSheetView>
-  </customSheetViews>
   <mergeCells count="35">
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A26:C26"/>
